--- a/utils/monday_sprint_2023-t2.xlsx
+++ b/utils/monday_sprint_2023-t2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="97">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Abertura</t>
+    <t>Entrada Sprint</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,6 +51,9 @@
     <t>Status</t>
   </si>
   <si>
+    <t>SLA (15 dias)</t>
+  </si>
+  <si>
     <t>Semana</t>
   </si>
   <si>
@@ -60,120 +63,171 @@
     <t>4775</t>
   </si>
   <si>
+    <t>Setor não informado</t>
+  </si>
+  <si>
+    <t>Novo Recurso</t>
+  </si>
+  <si>
+    <t>Categoria não informada</t>
+  </si>
+  <si>
+    <t>Movimentação Automática Inspeção</t>
+  </si>
+  <si>
+    <t>Baixa</t>
+  </si>
+  <si>
+    <t>Solicitante não informado</t>
+  </si>
+  <si>
+    <t>Equipe não informada</t>
+  </si>
+  <si>
+    <t>20/06/2021</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Fila</t>
+  </si>
+  <si>
+    <t>Aberto</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
+  </si>
+  <si>
+    <t>Junho</t>
+  </si>
+  <si>
+    <t>6680</t>
+  </si>
+  <si>
+    <t>Controle de alteração de fluxo de produção</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Em Análise</t>
+  </si>
+  <si>
+    <t>10080</t>
+  </si>
+  <si>
+    <t>Formato de sequência exclusivo para pré produtivo e ACVO</t>
+  </si>
+  <si>
+    <t>14/10/2021</t>
+  </si>
+  <si>
+    <t>Semana 2</t>
+  </si>
+  <si>
+    <t>Outubro</t>
+  </si>
+  <si>
+    <t>16019</t>
+  </si>
+  <si>
+    <t>Controle de frequência de atividades</t>
+  </si>
+  <si>
+    <t>12/07/2022</t>
+  </si>
+  <si>
+    <t>Julho</t>
+  </si>
+  <si>
+    <t>14540</t>
+  </si>
+  <si>
+    <t>Melhoria</t>
+  </si>
+  <si>
+    <t>Alteração Sistema de Orçamento (SAC 62414)</t>
+  </si>
+  <si>
+    <t>19/07/2022</t>
+  </si>
+  <si>
+    <t>Impedimento</t>
+  </si>
+  <si>
+    <t>3174817126</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Bloqueio de acesso a informações da carteira</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>01/09/2022</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
+    <t>Setembro</t>
+  </si>
+  <si>
+    <t>14430</t>
+  </si>
+  <si>
+    <t>Retirada do depósito a partir de romaneio</t>
+  </si>
+  <si>
+    <t>15/09/2022</t>
+  </si>
+  <si>
+    <t>16658</t>
+  </si>
+  <si>
+    <t>Priorizar emissão em série de sequências</t>
+  </si>
+  <si>
+    <t>28/10/2022</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
+    <t>16703</t>
+  </si>
+  <si>
+    <t>Unificar processo de baixa de saldo do depósito e estorno de sequências</t>
+  </si>
+  <si>
+    <t>Não definida</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Revisão de contador de linhas</t>
+  </si>
+  <si>
+    <t>31/10/2022</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
+  </si>
+  <si>
+    <t>Dashboard de Change Log - Governança de TI</t>
+  </si>
+  <si>
+    <t>Período</t>
+  </si>
+  <si>
     <t>2023-T2</t>
   </si>
   <si>
-    <t>Novo Recurso</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Movimentação Automática Inspeção</t>
-  </si>
-  <si>
-    <t>Baixa</t>
-  </si>
-  <si>
-    <t>Fila</t>
-  </si>
-  <si>
-    <t>Semana 3</t>
-  </si>
-  <si>
-    <t>6680</t>
-  </si>
-  <si>
-    <t>Controle de alteração de fluxo de produção</t>
-  </si>
-  <si>
-    <t>Média</t>
-  </si>
-  <si>
-    <t>Em Análise</t>
-  </si>
-  <si>
-    <t>10080</t>
-  </si>
-  <si>
-    <t>Formato de sequência exclusivo para pré produtivo e ACVO</t>
-  </si>
-  <si>
-    <t>Semana 2</t>
-  </si>
-  <si>
-    <t>16019</t>
-  </si>
-  <si>
-    <t>Controle de frequência de atividades</t>
-  </si>
-  <si>
-    <t>14540</t>
-  </si>
-  <si>
-    <t>Melhoria</t>
-  </si>
-  <si>
-    <t>Alteração Sistema de Orçamento (SAC 62414)</t>
-  </si>
-  <si>
-    <t>Impedimento</t>
-  </si>
-  <si>
-    <t>3174817126</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>Bloqueio de acesso a informações da carteira</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Semana 1</t>
-  </si>
-  <si>
-    <t>14430</t>
-  </si>
-  <si>
-    <t>Retirada do depósito a partir de romaneio</t>
-  </si>
-  <si>
-    <t>16658</t>
-  </si>
-  <si>
-    <t>Priorizar emissão em série de sequências</t>
-  </si>
-  <si>
-    <t>Semana 4</t>
-  </si>
-  <si>
-    <t>16703</t>
-  </si>
-  <si>
-    <t>Unificar processo de baixa de saldo do depósito e estorno de sequências</t>
-  </si>
-  <si>
-    <t>Não definida</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>Revisão de contador de linhas</t>
-  </si>
-  <si>
-    <t>Semana 5</t>
-  </si>
-  <si>
-    <t>Dashboard de Change Log - Governança de TI</t>
-  </si>
-  <si>
-    <t>Período</t>
-  </si>
-  <si>
     <t>Base</t>
   </si>
   <si>
@@ -213,7 +267,7 @@
     <t>Distribuição por Tipo</t>
   </si>
   <si>
-    <t>Cumprimento SLA</t>
+    <t>Cumprimento SLA (15 dias)</t>
   </si>
   <si>
     <t>Status Final</t>
@@ -235,6 +289,9 @@
   </si>
   <si>
     <t>A fazer</t>
+  </si>
+  <si>
+    <t>Abertos</t>
   </si>
   <si>
     <t>Fazendo</t>
@@ -663,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -673,13 +730,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="25" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="11" width="14" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -722,445 +781,478 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="J10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="C11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="N11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="O11" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1176,23 +1268,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -1200,16 +1292,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1228,12 +1320,12 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -1241,7 +1333,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1249,7 +1341,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -1267,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1280,12 +1372,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -1309,54 +1401,54 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10">
         <v>5</v>
       </c>
       <c r="G10" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -1364,25 +1456,25 @@
     </row>
     <row r="11" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="K11">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -1390,19 +1482,25 @@
     </row>
     <row r="12" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E12">
         <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H12">
         <v>6</v>
       </c>
+      <c r="J12" t="s">
+        <v>92</v>
+      </c>
+      <c r="K12">
+        <v>10</v>
+      </c>
       <c r="M12" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -1410,13 +1508,13 @@
     </row>
     <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H13">
         <v>2</v>
       </c>
       <c r="M13" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -1424,13 +1522,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -1438,7 +1536,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -1446,7 +1544,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N16">
         <v>4</v>
@@ -1454,7 +1552,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="N17">
         <v>5</v>
@@ -1462,7 +1560,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -1473,150 +1571,10 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" s="2">
-        <v>0</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25" s="2">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" s="2">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D27" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F27" s="2">
-        <v>0</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D28" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F28" s="2">
-        <v>0</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D29" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_2023-t2.xlsx
+++ b/utils/monday_sprint_2023-t2.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="95">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>4775</t>
+    <t>1407234942</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,22 +87,19 @@
     <t>20/06/2021</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>Não</t>
   </si>
   <si>
     <t>Fila</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
     <t>Semana 3</t>
   </si>
   <si>
     <t>Junho</t>
   </si>
   <si>
-    <t>6680</t>
+    <t>1407235060</t>
   </si>
   <si>
     <t>Controle de alteração de fluxo de produção</t>
@@ -114,7 +111,7 @@
     <t>Em Análise</t>
   </si>
   <si>
-    <t>10080</t>
+    <t>1787262235</t>
   </si>
   <si>
     <t>Formato de sequência exclusivo para pré produtivo e ACVO</t>
@@ -129,7 +126,7 @@
     <t>Outubro</t>
   </si>
   <si>
-    <t>16019</t>
+    <t>2930982228</t>
   </si>
   <si>
     <t>Controle de frequência de atividades</t>
@@ -141,7 +138,7 @@
     <t>Julho</t>
   </si>
   <si>
-    <t>14540</t>
+    <t>2961154730</t>
   </si>
   <si>
     <t>Melhoria</t>
@@ -177,7 +174,7 @@
     <t>Setembro</t>
   </si>
   <si>
-    <t>14430</t>
+    <t>3240144186</t>
   </si>
   <si>
     <t>Retirada do depósito a partir de romaneio</t>
@@ -186,7 +183,7 @@
     <t>15/09/2022</t>
   </si>
   <si>
-    <t>16658</t>
+    <t>3444199664</t>
   </si>
   <si>
     <t>Priorizar emissão em série de sequências</t>
@@ -198,7 +195,7 @@
     <t>Semana 4</t>
   </si>
   <si>
-    <t>16703</t>
+    <t>3444221276</t>
   </si>
   <si>
     <t>Unificar processo de baixa de saldo do depósito e estorno de sequências</t>
@@ -207,7 +204,7 @@
     <t>Não definida</t>
   </si>
   <si>
-    <t>TBD</t>
+    <t>3450955587</t>
   </si>
   <si>
     <t>Revisão de contador de linhas</t>
@@ -225,7 +222,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>2023-T2</t>
+    <t>Jun/2021</t>
   </si>
   <si>
     <t>Base</t>
@@ -283,9 +280,6 @@
   </si>
   <si>
     <t>Sim</t>
-  </si>
-  <si>
-    <t>Não</t>
   </si>
   <si>
     <t>A fazer</t>
@@ -823,18 +817,18 @@
         <v>25</v>
       </c>
       <c r="M2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>16</v>
@@ -846,13 +840,13 @@
         <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>21</v>
@@ -867,21 +861,21 @@
         <v>24</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -893,10 +887,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -908,27 +902,27 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -940,13 +934,13 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>21</v>
@@ -955,7 +949,7 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>24</v>
@@ -964,36 +958,36 @@
         <v>25</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>21</v>
@@ -1002,45 +996,45 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="M6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="O6" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>21</v>
@@ -1049,45 +1043,45 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>21</v>
@@ -1096,45 +1090,45 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="O8" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>21</v>
@@ -1143,7 +1137,7 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>24</v>
@@ -1152,18 +1146,18 @@
         <v>25</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1175,13 +1169,13 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>21</v>
@@ -1190,45 +1184,45 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="O10" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>21</v>
@@ -1237,7 +1231,7 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>24</v>
@@ -1246,13 +1240,13 @@
         <v>25</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1268,23 +1262,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" t="s">
         <v>69</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>70</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>71</v>
-      </c>
-      <c r="E2" t="s">
-        <v>72</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -1292,16 +1286,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1320,12 +1314,12 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -1333,7 +1327,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1341,7 +1335,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -1359,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1372,12 +1366,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -1401,25 +1395,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="M9" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="P9" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="P9" s="6" t="s">
+      <c r="Q9" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="Q9" s="6" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -1436,19 +1430,19 @@
         <v>5</v>
       </c>
       <c r="G10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -1456,25 +1450,25 @@
     </row>
     <row r="11" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -1482,25 +1476,25 @@
     </row>
     <row r="12" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E12">
         <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H12">
         <v>6</v>
       </c>
       <c r="J12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K12">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -1514,7 +1508,7 @@
         <v>2</v>
       </c>
       <c r="M13" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -1522,13 +1516,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -1536,7 +1530,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -1552,7 +1546,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N17">
         <v>5</v>
@@ -1560,10 +1554,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -1571,10 +1565,150 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1809</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1809</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1809</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1809</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1809</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1809</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D27" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1809</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1809</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D29" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1809</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D30" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1809</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
